--- a/Sales Reporting PPL - Rana Bilal Lahore (1).xlsx
+++ b/Sales Reporting PPL - Rana Bilal Lahore (1).xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B71F57-5176-44FA-926F-EE3D01893D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC0D2BE-8C6B-4C00-B1C7-048876A01C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="(23-06-26)" sheetId="3" r:id="rId1"/>
-    <sheet name="(22-06-26)" sheetId="1" r:id="rId2"/>
+    <sheet name="(24-06-26)" sheetId="4" r:id="rId1"/>
+    <sheet name="(23-06-26)" sheetId="3" r:id="rId2"/>
+    <sheet name="(22-06-26)" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="53">
   <si>
     <t>Booking</t>
   </si>
@@ -177,6 +178,15 @@
   <si>
     <t>23-06-26</t>
   </si>
+  <si>
+    <t xml:space="preserve">Pending For Monday </t>
+  </si>
+  <si>
+    <t>Area Closed</t>
+  </si>
+  <si>
+    <t>24-06-26</t>
+  </si>
 </sst>
 </file>
 
@@ -635,7 +645,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -813,6 +823,39 @@
     <xf numFmtId="164" fontId="0" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -835,33 +878,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1144,6 +1160,1933 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C5516F7-6F3B-4807-80F6-5003860986DF}">
+  <dimension ref="A1:W26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.1796875" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.7265625" customWidth="1"/>
+    <col min="20" max="21" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
+    </row>
+    <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E2" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="R3" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="40">
+        <v>50</v>
+      </c>
+      <c r="H4" s="54">
+        <v>11</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" ref="I4:I26" si="0">H4/G4</f>
+        <v>0.22</v>
+      </c>
+      <c r="J4" s="44">
+        <v>40</v>
+      </c>
+      <c r="K4" s="57">
+        <v>9.75</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" ref="L4:L24" si="1">K4/J4</f>
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="M4" s="11">
+        <f t="shared" ref="M4:N13" si="2">K4/H4</f>
+        <v>0.88636363636363635</v>
+      </c>
+      <c r="N4" s="12">
+        <f t="shared" si="2"/>
+        <v>1.1079545454545454</v>
+      </c>
+      <c r="O4" s="46">
+        <f>H4</f>
+        <v>11</v>
+      </c>
+      <c r="P4" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="10">
+        <f t="shared" ref="Q4:Q26" si="3">P4/O4</f>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="R4" s="58">
+        <f>K4</f>
+        <v>9.75</v>
+      </c>
+      <c r="S4" s="59">
+        <v>7.5</v>
+      </c>
+      <c r="T4" s="10">
+        <f t="shared" ref="T4:T13" si="4">S4/R4</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U4" s="11">
+        <f t="shared" ref="U4:V13" si="5">S4/P4</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="V4" s="12">
+        <f t="shared" si="5"/>
+        <v>0.94017094017094016</v>
+      </c>
+      <c r="W4" s="12"/>
+    </row>
+    <row r="5" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="41">
+        <v>50</v>
+      </c>
+      <c r="H5" s="55">
+        <v>7</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J5" s="45">
+        <v>30</v>
+      </c>
+      <c r="K5" s="60">
+        <v>7.5</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="M5" s="16">
+        <f t="shared" si="2"/>
+        <v>1.0714285714285714</v>
+      </c>
+      <c r="N5" s="17">
+        <f t="shared" si="2"/>
+        <v>1.7857142857142856</v>
+      </c>
+      <c r="O5" s="46">
+        <f t="shared" ref="O5:O13" si="6">H5</f>
+        <v>7</v>
+      </c>
+      <c r="P5" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="R5" s="58">
+        <f t="shared" ref="R5:R13" si="7">K5</f>
+        <v>7.5</v>
+      </c>
+      <c r="S5" s="61">
+        <v>6.5</v>
+      </c>
+      <c r="T5" s="15">
+        <f t="shared" si="4"/>
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="U5" s="16">
+        <f t="shared" si="5"/>
+        <v>1.3</v>
+      </c>
+      <c r="V5" s="17">
+        <f t="shared" si="5"/>
+        <v>1.2133333333333334</v>
+      </c>
+      <c r="W5" s="17"/>
+    </row>
+    <row r="6" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="41">
+        <v>50</v>
+      </c>
+      <c r="H6" s="55">
+        <v>6</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="J6" s="45">
+        <v>25</v>
+      </c>
+      <c r="K6" s="60">
+        <v>7.35</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="1"/>
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="M6" s="16">
+        <f t="shared" si="2"/>
+        <v>1.2249999999999999</v>
+      </c>
+      <c r="N6" s="17">
+        <f t="shared" si="2"/>
+        <v>2.4499999999999997</v>
+      </c>
+      <c r="O6" s="46">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="P6" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="58">
+        <f t="shared" si="7"/>
+        <v>7.35</v>
+      </c>
+      <c r="S6" s="61">
+        <v>0</v>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U6" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="41">
+        <v>50</v>
+      </c>
+      <c r="H7" s="55">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="45">
+        <v>30</v>
+      </c>
+      <c r="K7" s="60">
+        <v>0</v>
+      </c>
+      <c r="L7" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O7" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R7" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="61">
+        <v>0</v>
+      </c>
+      <c r="T7" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W7" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="41">
+        <v>50</v>
+      </c>
+      <c r="H8" s="55">
+        <v>6</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+      <c r="J8" s="45">
+        <v>20</v>
+      </c>
+      <c r="K8" s="60">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="1"/>
+        <v>0.80749999999999988</v>
+      </c>
+      <c r="M8" s="16">
+        <f t="shared" si="2"/>
+        <v>2.6916666666666664</v>
+      </c>
+      <c r="N8" s="17">
+        <f t="shared" si="2"/>
+        <v>6.7291666666666661</v>
+      </c>
+      <c r="O8" s="46">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="P8" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="15">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="R8" s="58">
+        <f t="shared" si="7"/>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="S8" s="61">
+        <v>8</v>
+      </c>
+      <c r="T8" s="15">
+        <f t="shared" si="4"/>
+        <v>0.49535603715170284</v>
+      </c>
+      <c r="U8" s="16">
+        <f t="shared" si="5"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="V8" s="17">
+        <f t="shared" si="5"/>
+        <v>0.99071207430340569</v>
+      </c>
+      <c r="W8" s="17"/>
+    </row>
+    <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="41">
+        <v>0</v>
+      </c>
+      <c r="H9" s="55">
+        <v>6</v>
+      </c>
+      <c r="I9" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="45">
+        <v>20</v>
+      </c>
+      <c r="K9" s="60">
+        <v>5.5</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="1"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="M9" s="16">
+        <f t="shared" si="2"/>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="N9" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O9" s="46">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="P9" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="15">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="R9" s="58">
+        <f t="shared" si="7"/>
+        <v>5.5</v>
+      </c>
+      <c r="S9" s="61">
+        <v>3.45</v>
+      </c>
+      <c r="T9" s="15">
+        <f t="shared" si="4"/>
+        <v>0.62727272727272732</v>
+      </c>
+      <c r="U9" s="16">
+        <f t="shared" si="5"/>
+        <v>1.1500000000000001</v>
+      </c>
+      <c r="V9" s="17">
+        <f t="shared" si="5"/>
+        <v>1.2545454545454546</v>
+      </c>
+      <c r="W9" s="17"/>
+    </row>
+    <row r="10" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="41">
+        <v>0</v>
+      </c>
+      <c r="H10" s="55">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="45">
+        <v>0</v>
+      </c>
+      <c r="K10" s="60">
+        <v>0</v>
+      </c>
+      <c r="L10" s="15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="61"/>
+      <c r="T10" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W10" s="17"/>
+    </row>
+    <row r="11" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="41">
+        <v>10</v>
+      </c>
+      <c r="H11" s="55">
+        <v>10</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="45">
+        <v>220</v>
+      </c>
+      <c r="K11" s="60">
+        <v>200</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="1"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="M11" s="16">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="N11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="O11" s="46">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="P11" s="43">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="15">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="R11" s="58">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="S11" s="61">
+        <v>56</v>
+      </c>
+      <c r="T11" s="15">
+        <f t="shared" si="4"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U11" s="16">
+        <f t="shared" si="5"/>
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="V11" s="17">
+        <f t="shared" si="5"/>
+        <v>0.46666666666666673</v>
+      </c>
+      <c r="W11" s="17"/>
+    </row>
+    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="41">
+        <v>50</v>
+      </c>
+      <c r="H12" s="55">
+        <v>16</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
+      <c r="J12" s="45">
+        <v>30</v>
+      </c>
+      <c r="K12" s="60">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="M12" s="16">
+        <f t="shared" si="2"/>
+        <v>1.3125</v>
+      </c>
+      <c r="N12" s="17">
+        <f t="shared" si="2"/>
+        <v>2.1875</v>
+      </c>
+      <c r="O12" s="46">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="58">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="S12" s="61"/>
+      <c r="T12" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V12" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W12" s="17"/>
+    </row>
+    <row r="13" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="41">
+        <v>0</v>
+      </c>
+      <c r="H13" s="55">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J13" s="45">
+        <v>0</v>
+      </c>
+      <c r="K13" s="60">
+        <v>0</v>
+      </c>
+      <c r="L13" s="15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M13" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O13" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R13" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="61">
+        <v>0</v>
+      </c>
+      <c r="T13" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W13" s="17"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="18">
+        <f>SUM(G4:G13)</f>
+        <v>310</v>
+      </c>
+      <c r="H14" s="19">
+        <f t="shared" ref="H14:K14" si="8">SUM(H4:H13)</f>
+        <v>62</v>
+      </c>
+      <c r="I14" s="20">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J14" s="21">
+        <f t="shared" si="8"/>
+        <v>415</v>
+      </c>
+      <c r="K14" s="63">
+        <f t="shared" si="8"/>
+        <v>267.25</v>
+      </c>
+      <c r="L14" s="20">
+        <f>K14/J14</f>
+        <v>0.64397590361445778</v>
+      </c>
+      <c r="M14" s="21">
+        <f>K14/H14</f>
+        <v>4.310483870967742</v>
+      </c>
+      <c r="N14" s="22" t="e">
+        <f>AVERAGE(N4:N13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O14" s="18">
+        <f>SUM(O4:O13)</f>
+        <v>62</v>
+      </c>
+      <c r="P14" s="19">
+        <f t="shared" ref="P14" si="9">SUM(P4:P13)</f>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="20">
+        <f t="shared" si="3"/>
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="R14" s="64">
+        <f t="shared" ref="R14:S14" si="10">SUM(R4:R13)</f>
+        <v>267.25</v>
+      </c>
+      <c r="S14" s="63">
+        <f t="shared" si="10"/>
+        <v>81.45</v>
+      </c>
+      <c r="T14" s="20">
+        <f>S14/R14</f>
+        <v>0.30477081384471472</v>
+      </c>
+      <c r="U14" s="21">
+        <f>S14/P14</f>
+        <v>3.1326923076923077</v>
+      </c>
+      <c r="V14" s="22" t="e">
+        <f>AVERAGE(V4:V13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W14" s="22"/>
+    </row>
+    <row r="15" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="41">
+        <v>50</v>
+      </c>
+      <c r="H15" s="55">
+        <v>17</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>0.34</v>
+      </c>
+      <c r="J15" s="45">
+        <v>30</v>
+      </c>
+      <c r="K15" s="60"/>
+      <c r="L15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
+        <f t="shared" ref="M15:M19" si="11">K15/H15</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="17">
+        <v>1</v>
+      </c>
+      <c r="O15" s="47">
+        <f>H15</f>
+        <v>17</v>
+      </c>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="62">
+        <f>K15</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="61"/>
+      <c r="T15" s="15" t="e">
+        <f t="shared" ref="T15:T19" si="12">S15/R15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="16" t="e">
+        <f t="shared" ref="U15:U19" si="13">S15/P15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" s="17">
+        <v>1</v>
+      </c>
+      <c r="W15" s="17"/>
+    </row>
+    <row r="16" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="41">
+        <v>50</v>
+      </c>
+      <c r="H16" s="55">
+        <v>15</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="J16" s="45">
+        <v>30</v>
+      </c>
+      <c r="K16" s="60"/>
+      <c r="L16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>1</v>
+      </c>
+      <c r="O16" s="47">
+        <f t="shared" ref="O16:O19" si="14">H16</f>
+        <v>15</v>
+      </c>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="62">
+        <f t="shared" ref="R16:R19" si="15">K16</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="61"/>
+      <c r="T16" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" s="17">
+        <v>1</v>
+      </c>
+      <c r="W16" s="17"/>
+    </row>
+    <row r="17" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="41">
+        <v>50</v>
+      </c>
+      <c r="H17" s="55">
+        <v>14</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J17" s="45">
+        <v>30</v>
+      </c>
+      <c r="K17" s="60"/>
+      <c r="L17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="47">
+        <f t="shared" si="14"/>
+        <v>14</v>
+      </c>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="61"/>
+      <c r="T17" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" s="17">
+        <v>1</v>
+      </c>
+      <c r="W17" s="17"/>
+    </row>
+    <row r="18" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="41">
+        <v>50</v>
+      </c>
+      <c r="H18" s="55">
+        <v>17</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="0"/>
+        <v>0.34</v>
+      </c>
+      <c r="J18" s="45">
+        <v>30</v>
+      </c>
+      <c r="K18" s="60"/>
+      <c r="L18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="17">
+        <v>1</v>
+      </c>
+      <c r="O18" s="47">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="61"/>
+      <c r="T18" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V18" s="17">
+        <v>1</v>
+      </c>
+      <c r="W18" s="17"/>
+    </row>
+    <row r="19" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="41">
+        <v>50</v>
+      </c>
+      <c r="H19" s="55">
+        <v>10</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J19" s="45">
+        <v>30</v>
+      </c>
+      <c r="K19" s="60"/>
+      <c r="L19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="17">
+        <v>1</v>
+      </c>
+      <c r="O19" s="47">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="61"/>
+      <c r="T19" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V19" s="17">
+        <v>1</v>
+      </c>
+      <c r="W19" s="17"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="18">
+        <f>SUM(G15:G19)</f>
+        <v>250</v>
+      </c>
+      <c r="H20" s="19">
+        <f t="shared" ref="H20:K20" si="16">SUM(H15:H19)</f>
+        <v>73</v>
+      </c>
+      <c r="I20" s="20">
+        <f t="shared" si="0"/>
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="J20" s="21">
+        <f t="shared" si="16"/>
+        <v>150</v>
+      </c>
+      <c r="K20" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="20">
+        <f>K20/J20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="21">
+        <f>K20/H20</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="22">
+        <f>AVERAGE(N15:N19)</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="18">
+        <f>SUM(O15:O19)</f>
+        <v>73</v>
+      </c>
+      <c r="P20" s="19">
+        <f t="shared" ref="P20" si="17">SUM(P15:P19)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="56">
+        <f t="shared" ref="R20:S20" si="18">SUM(R15:R19)</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="19">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="20" t="e">
+        <f>S20/R20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="21" t="e">
+        <f>S20/P20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" s="22">
+        <f>AVERAGE(V15:V19)</f>
+        <v>1</v>
+      </c>
+      <c r="W20" s="22"/>
+    </row>
+    <row r="21" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="41">
+        <v>50</v>
+      </c>
+      <c r="H21" s="55">
+        <v>14</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J21" s="45">
+        <v>60</v>
+      </c>
+      <c r="K21" s="60">
+        <v>25</v>
+      </c>
+      <c r="L21" s="15">
+        <f t="shared" si="1"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M21" s="16">
+        <f t="shared" ref="M21:M24" si="19">K21/H21</f>
+        <v>1.7857142857142858</v>
+      </c>
+      <c r="N21" s="17">
+        <v>1</v>
+      </c>
+      <c r="O21" s="47">
+        <f>H21</f>
+        <v>14</v>
+      </c>
+      <c r="P21" s="43">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="15">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="R21" s="62">
+        <f>K21</f>
+        <v>25</v>
+      </c>
+      <c r="S21" s="61">
+        <v>15</v>
+      </c>
+      <c r="T21" s="15">
+        <f t="shared" ref="T21:T24" si="20">S21/R21</f>
+        <v>0.6</v>
+      </c>
+      <c r="U21" s="16">
+        <f t="shared" ref="U21:U24" si="21">S21/P21</f>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="V21" s="17">
+        <v>1</v>
+      </c>
+      <c r="W21" s="17"/>
+    </row>
+    <row r="22" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="41">
+        <v>50</v>
+      </c>
+      <c r="H22" s="55">
+        <v>4</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J22" s="45">
+        <v>40</v>
+      </c>
+      <c r="K22" s="60">
+        <v>7</v>
+      </c>
+      <c r="L22" s="15">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M22" s="16">
+        <f t="shared" si="19"/>
+        <v>1.75</v>
+      </c>
+      <c r="N22" s="17">
+        <v>1</v>
+      </c>
+      <c r="O22" s="47">
+        <f t="shared" ref="O22:O24" si="22">H22</f>
+        <v>4</v>
+      </c>
+      <c r="P22" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="15">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="R22" s="62">
+        <f t="shared" ref="R22:R24" si="23">K22</f>
+        <v>7</v>
+      </c>
+      <c r="S22" s="61">
+        <v>6</v>
+      </c>
+      <c r="T22" s="15">
+        <f t="shared" si="20"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U22" s="16">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="V22" s="17">
+        <v>1</v>
+      </c>
+      <c r="W22" s="17"/>
+    </row>
+    <row r="23" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="41">
+        <v>50</v>
+      </c>
+      <c r="H23" s="55">
+        <v>4</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J23" s="45">
+        <v>40</v>
+      </c>
+      <c r="K23" s="60">
+        <v>7</v>
+      </c>
+      <c r="L23" s="15">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M23" s="16">
+        <f t="shared" si="19"/>
+        <v>1.75</v>
+      </c>
+      <c r="N23" s="17">
+        <v>1</v>
+      </c>
+      <c r="O23" s="47">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="P23" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="15">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="R23" s="62">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="S23" s="61">
+        <v>4</v>
+      </c>
+      <c r="T23" s="15">
+        <f t="shared" si="20"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U23" s="16">
+        <f t="shared" si="21"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="V23" s="17">
+        <v>1</v>
+      </c>
+      <c r="W23" s="17"/>
+    </row>
+    <row r="24" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="41">
+        <v>50</v>
+      </c>
+      <c r="H24" s="55">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="45">
+        <v>30</v>
+      </c>
+      <c r="K24" s="60">
+        <v>0</v>
+      </c>
+      <c r="L24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="16" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="17">
+        <v>1</v>
+      </c>
+      <c r="O24" s="47">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R24" s="62">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="61">
+        <v>0</v>
+      </c>
+      <c r="T24" s="15" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="16" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V24" s="17">
+        <v>1</v>
+      </c>
+      <c r="W24" s="17"/>
+    </row>
+    <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="23">
+        <f>SUM(G21:G24)</f>
+        <v>200</v>
+      </c>
+      <c r="H25" s="24">
+        <f t="shared" ref="H25:K25" si="24">SUM(H21:H24)</f>
+        <v>22</v>
+      </c>
+      <c r="I25" s="25">
+        <f t="shared" si="0"/>
+        <v>0.11</v>
+      </c>
+      <c r="J25" s="26">
+        <f t="shared" si="24"/>
+        <v>170</v>
+      </c>
+      <c r="K25" s="24">
+        <f t="shared" si="24"/>
+        <v>39</v>
+      </c>
+      <c r="L25" s="25">
+        <f>K25/J25</f>
+        <v>0.22941176470588234</v>
+      </c>
+      <c r="M25" s="26">
+        <f>K25/H25</f>
+        <v>1.7727272727272727</v>
+      </c>
+      <c r="N25" s="27">
+        <f>AVERAGE(N21:N24)</f>
+        <v>1</v>
+      </c>
+      <c r="O25" s="23">
+        <f>SUM(O21:O24)</f>
+        <v>22</v>
+      </c>
+      <c r="P25" s="24">
+        <f t="shared" ref="P25" si="25">SUM(P21:P24)</f>
+        <v>13</v>
+      </c>
+      <c r="Q25" s="25">
+        <f t="shared" si="3"/>
+        <v>0.59090909090909094</v>
+      </c>
+      <c r="R25" s="26">
+        <f t="shared" ref="R25:S25" si="26">SUM(R21:R24)</f>
+        <v>39</v>
+      </c>
+      <c r="S25" s="24">
+        <f t="shared" si="26"/>
+        <v>25</v>
+      </c>
+      <c r="T25" s="25">
+        <f>S25/R25</f>
+        <v>0.64102564102564108</v>
+      </c>
+      <c r="U25" s="26">
+        <f>S25/P25</f>
+        <v>1.9230769230769231</v>
+      </c>
+      <c r="V25" s="27">
+        <f>AVERAGE(V21:V24)</f>
+        <v>1</v>
+      </c>
+      <c r="W25" s="27"/>
+    </row>
+    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="34">
+        <f>+G25+G20+G14</f>
+        <v>760</v>
+      </c>
+      <c r="H26" s="35">
+        <f t="shared" ref="H26:K26" si="27">+H25+H20+H14</f>
+        <v>157</v>
+      </c>
+      <c r="I26" s="36">
+        <f t="shared" si="0"/>
+        <v>0.20657894736842106</v>
+      </c>
+      <c r="J26" s="37">
+        <f t="shared" si="27"/>
+        <v>735</v>
+      </c>
+      <c r="K26" s="35">
+        <f t="shared" si="27"/>
+        <v>306.25</v>
+      </c>
+      <c r="L26" s="36">
+        <f>K26/J26</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M26" s="37">
+        <f>K26/H26</f>
+        <v>1.9506369426751593</v>
+      </c>
+      <c r="N26" s="38"/>
+      <c r="O26" s="34">
+        <f>+O25+O20+O14</f>
+        <v>157</v>
+      </c>
+      <c r="P26" s="35">
+        <f t="shared" ref="P26" si="28">+P25+P20+P14</f>
+        <v>39</v>
+      </c>
+      <c r="Q26" s="36">
+        <f t="shared" si="3"/>
+        <v>0.24840764331210191</v>
+      </c>
+      <c r="R26" s="37">
+        <f t="shared" ref="R26:S26" si="29">+R25+R20+R14</f>
+        <v>306.25</v>
+      </c>
+      <c r="S26" s="35">
+        <f t="shared" si="29"/>
+        <v>106.45</v>
+      </c>
+      <c r="T26" s="36">
+        <f>S26/R26</f>
+        <v>0.3475918367346939</v>
+      </c>
+      <c r="U26" s="37">
+        <f>S26/P26</f>
+        <v>2.7294871794871796</v>
+      </c>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C674A7-3942-47E0-8E65-980F1C82B5F1}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1167,54 +3110,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="65"/>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="69" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="69"/>
-      <c r="L2" s="70"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="68" t="s">
+      <c r="O2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="69" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="69"/>
-      <c r="T2" s="70"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -2081,11 +4024,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -2547,11 +4490,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -2936,11 +4879,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -3011,13 +4954,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>
@@ -3096,7 +5039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3120,54 +5063,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="65"/>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="69"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="69" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="69"/>
-      <c r="L2" s="70"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="68" t="s">
+      <c r="O2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="69" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="69"/>
-      <c r="T2" s="70"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -4042,11 +5985,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="71" t="s">
+      <c r="D14" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -4498,11 +6441,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -4879,11 +6822,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -4954,13 +6897,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>

--- a/Sales Reporting PPL - Rana Bilal Lahore (1).xlsx
+++ b/Sales Reporting PPL - Rana Bilal Lahore (1).xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC0D2BE-8C6B-4C00-B1C7-048876A01C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AB3236-7793-4FDE-8F79-EAA58159FAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="(24-06-26)" sheetId="4" r:id="rId1"/>
-    <sheet name="(23-06-26)" sheetId="3" r:id="rId2"/>
-    <sheet name="(22-06-26)" sheetId="1" r:id="rId3"/>
+    <sheet name="(25-06-26)" sheetId="5" r:id="rId1"/>
+    <sheet name="(24-06-26)" sheetId="4" r:id="rId2"/>
+    <sheet name="(23-06-26)" sheetId="3" r:id="rId3"/>
+    <sheet name="(22-06-26)" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="54">
   <si>
     <t>Booking</t>
   </si>
@@ -186,6 +187,9 @@
   </si>
   <si>
     <t>24-06-26</t>
+  </si>
+  <si>
+    <t>25-06-26</t>
   </si>
 </sst>
 </file>
@@ -829,6 +833,30 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -854,30 +882,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1160,6 +1164,1927 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB43984-EA48-457F-9A17-F0D733832855}">
+  <dimension ref="A1:W26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.1796875" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.7265625" customWidth="1"/>
+    <col min="20" max="21" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="67"/>
+    </row>
+    <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E2" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="69"/>
+      <c r="G2" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="71"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="71"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="R3" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="40">
+        <v>50</v>
+      </c>
+      <c r="H4" s="54">
+        <v>7</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" ref="I4:I26" si="0">H4/G4</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J4" s="44">
+        <v>40</v>
+      </c>
+      <c r="K4" s="57">
+        <v>14.25</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" ref="L4:L24" si="1">K4/J4</f>
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="M4" s="11">
+        <f t="shared" ref="M4:N13" si="2">K4/H4</f>
+        <v>2.0357142857142856</v>
+      </c>
+      <c r="N4" s="12">
+        <f t="shared" si="2"/>
+        <v>2.5446428571428568</v>
+      </c>
+      <c r="O4" s="46">
+        <f>H4</f>
+        <v>7</v>
+      </c>
+      <c r="P4" s="42">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="10">
+        <f t="shared" ref="Q4:Q26" si="3">P4/O4</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R4" s="58">
+        <f>K4</f>
+        <v>14.25</v>
+      </c>
+      <c r="S4" s="59">
+        <v>4</v>
+      </c>
+      <c r="T4" s="10">
+        <f t="shared" ref="T4:T13" si="4">S4/R4</f>
+        <v>0.2807017543859649</v>
+      </c>
+      <c r="U4" s="11">
+        <f t="shared" ref="U4:V13" si="5">S4/P4</f>
+        <v>2</v>
+      </c>
+      <c r="V4" s="12">
+        <f t="shared" si="5"/>
+        <v>0.98245614035087714</v>
+      </c>
+      <c r="W4" s="12"/>
+    </row>
+    <row r="5" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="41">
+        <v>50</v>
+      </c>
+      <c r="H5" s="55">
+        <v>5</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="45">
+        <v>30</v>
+      </c>
+      <c r="K5" s="60">
+        <v>5.7</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="1"/>
+        <v>0.19</v>
+      </c>
+      <c r="M5" s="16">
+        <f t="shared" si="2"/>
+        <v>1.1400000000000001</v>
+      </c>
+      <c r="N5" s="17">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
+      </c>
+      <c r="O5" s="46">
+        <f t="shared" ref="O5:O13" si="6">H5</f>
+        <v>5</v>
+      </c>
+      <c r="P5" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="R5" s="58">
+        <f t="shared" ref="R5:R13" si="7">K5</f>
+        <v>5.7</v>
+      </c>
+      <c r="S5" s="61">
+        <v>4.7</v>
+      </c>
+      <c r="T5" s="15">
+        <f t="shared" si="4"/>
+        <v>0.82456140350877194</v>
+      </c>
+      <c r="U5" s="16">
+        <f t="shared" si="5"/>
+        <v>1.5666666666666667</v>
+      </c>
+      <c r="V5" s="17">
+        <f t="shared" si="5"/>
+        <v>1.3742690058479532</v>
+      </c>
+      <c r="W5" s="17"/>
+    </row>
+    <row r="6" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="41">
+        <v>50</v>
+      </c>
+      <c r="H6" s="55">
+        <v>4</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J6" s="45">
+        <v>25</v>
+      </c>
+      <c r="K6" s="60">
+        <v>6.5</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="1"/>
+        <v>0.26</v>
+      </c>
+      <c r="M6" s="16">
+        <f t="shared" si="2"/>
+        <v>1.625</v>
+      </c>
+      <c r="N6" s="17">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="O6" s="46">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="P6" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="58">
+        <f t="shared" si="7"/>
+        <v>6.5</v>
+      </c>
+      <c r="S6" s="61">
+        <v>0</v>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U6" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="41">
+        <v>50</v>
+      </c>
+      <c r="H7" s="55">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="45">
+        <v>30</v>
+      </c>
+      <c r="K7" s="60">
+        <v>0</v>
+      </c>
+      <c r="L7" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O7" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R7" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="61">
+        <v>0</v>
+      </c>
+      <c r="T7" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W7" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="41">
+        <v>50</v>
+      </c>
+      <c r="H8" s="55">
+        <v>10</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J8" s="45">
+        <v>20</v>
+      </c>
+      <c r="K8" s="60">
+        <v>22.8</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="1"/>
+        <v>1.1400000000000001</v>
+      </c>
+      <c r="M8" s="16">
+        <f t="shared" si="2"/>
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="N8" s="17">
+        <f t="shared" si="2"/>
+        <v>5.7</v>
+      </c>
+      <c r="O8" s="46">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="P8" s="43">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="15">
+        <f t="shared" si="3"/>
+        <v>0.8</v>
+      </c>
+      <c r="R8" s="58">
+        <f t="shared" si="7"/>
+        <v>22.8</v>
+      </c>
+      <c r="S8" s="61">
+        <v>21.8</v>
+      </c>
+      <c r="T8" s="15">
+        <f t="shared" si="4"/>
+        <v>0.95614035087719296</v>
+      </c>
+      <c r="U8" s="16">
+        <f t="shared" si="5"/>
+        <v>2.7250000000000001</v>
+      </c>
+      <c r="V8" s="17">
+        <f t="shared" si="5"/>
+        <v>1.1951754385964912</v>
+      </c>
+      <c r="W8" s="17"/>
+    </row>
+    <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="41">
+        <v>0</v>
+      </c>
+      <c r="H9" s="55">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="45">
+        <v>20</v>
+      </c>
+      <c r="K9" s="60">
+        <v>0</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O9" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="61">
+        <v>0</v>
+      </c>
+      <c r="T9" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W9" s="17"/>
+    </row>
+    <row r="10" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="41">
+        <v>0</v>
+      </c>
+      <c r="H10" s="55">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="45">
+        <v>0</v>
+      </c>
+      <c r="K10" s="60">
+        <v>0</v>
+      </c>
+      <c r="L10" s="15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="61"/>
+      <c r="T10" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W10" s="17"/>
+    </row>
+    <row r="11" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="41">
+        <v>25</v>
+      </c>
+      <c r="H11" s="55">
+        <v>20</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J11" s="45">
+        <v>220</v>
+      </c>
+      <c r="K11" s="60">
+        <v>180</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="1"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="M11" s="16">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="N11" s="17">
+        <f t="shared" si="2"/>
+        <v>1.0227272727272727</v>
+      </c>
+      <c r="O11" s="46">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="P11" s="43">
+        <v>16</v>
+      </c>
+      <c r="Q11" s="15">
+        <f t="shared" si="3"/>
+        <v>0.8</v>
+      </c>
+      <c r="R11" s="58">
+        <f t="shared" si="7"/>
+        <v>180</v>
+      </c>
+      <c r="S11" s="61">
+        <v>131</v>
+      </c>
+      <c r="T11" s="15">
+        <f t="shared" si="4"/>
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="U11" s="16">
+        <f t="shared" si="5"/>
+        <v>8.1875</v>
+      </c>
+      <c r="V11" s="17">
+        <f t="shared" si="5"/>
+        <v>0.9097222222222221</v>
+      </c>
+      <c r="W11" s="17"/>
+    </row>
+    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="41">
+        <v>50</v>
+      </c>
+      <c r="H12" s="55">
+        <v>16</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
+      <c r="J12" s="45">
+        <v>30</v>
+      </c>
+      <c r="K12" s="60">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="M12" s="16">
+        <f t="shared" si="2"/>
+        <v>1.3125</v>
+      </c>
+      <c r="N12" s="17">
+        <f t="shared" si="2"/>
+        <v>2.1875</v>
+      </c>
+      <c r="O12" s="46">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="P12" s="43">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="15">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="R12" s="58">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="S12" s="61">
+        <v>21</v>
+      </c>
+      <c r="T12" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="U12" s="16">
+        <f t="shared" si="5"/>
+        <v>1.3125</v>
+      </c>
+      <c r="V12" s="17">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W12" s="17"/>
+    </row>
+    <row r="13" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="41">
+        <v>0</v>
+      </c>
+      <c r="H13" s="55">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J13" s="45">
+        <v>0</v>
+      </c>
+      <c r="K13" s="60">
+        <v>0</v>
+      </c>
+      <c r="L13" s="15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M13" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O13" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R13" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="61">
+        <v>0</v>
+      </c>
+      <c r="T13" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W13" s="17"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="18">
+        <f>SUM(G4:G13)</f>
+        <v>325</v>
+      </c>
+      <c r="H14" s="19">
+        <f t="shared" ref="H14:K14" si="8">SUM(H4:H13)</f>
+        <v>62</v>
+      </c>
+      <c r="I14" s="20">
+        <f t="shared" si="0"/>
+        <v>0.19076923076923077</v>
+      </c>
+      <c r="J14" s="21">
+        <f t="shared" si="8"/>
+        <v>415</v>
+      </c>
+      <c r="K14" s="63">
+        <f t="shared" si="8"/>
+        <v>250.25</v>
+      </c>
+      <c r="L14" s="20">
+        <f>K14/J14</f>
+        <v>0.6030120481927711</v>
+      </c>
+      <c r="M14" s="21">
+        <f>K14/H14</f>
+        <v>4.036290322580645</v>
+      </c>
+      <c r="N14" s="22" t="e">
+        <f>AVERAGE(N4:N13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O14" s="18">
+        <f>SUM(O4:O13)</f>
+        <v>62</v>
+      </c>
+      <c r="P14" s="19">
+        <f t="shared" ref="P14" si="9">SUM(P4:P13)</f>
+        <v>45</v>
+      </c>
+      <c r="Q14" s="20">
+        <f t="shared" si="3"/>
+        <v>0.72580645161290325</v>
+      </c>
+      <c r="R14" s="64">
+        <f t="shared" ref="R14:S14" si="10">SUM(R4:R13)</f>
+        <v>250.25</v>
+      </c>
+      <c r="S14" s="63">
+        <f t="shared" si="10"/>
+        <v>182.5</v>
+      </c>
+      <c r="T14" s="20">
+        <f>S14/R14</f>
+        <v>0.72927072927072922</v>
+      </c>
+      <c r="U14" s="21">
+        <f>S14/P14</f>
+        <v>4.0555555555555554</v>
+      </c>
+      <c r="V14" s="22" t="e">
+        <f>AVERAGE(V4:V13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W14" s="22"/>
+    </row>
+    <row r="15" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="41">
+        <v>50</v>
+      </c>
+      <c r="H15" s="55"/>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="45">
+        <v>30</v>
+      </c>
+      <c r="K15" s="60"/>
+      <c r="L15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="16" t="e">
+        <f t="shared" ref="M15:M19" si="11">K15/H15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N15" s="17">
+        <v>1</v>
+      </c>
+      <c r="O15" s="47">
+        <f>H15</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R15" s="62">
+        <f>K15</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="61"/>
+      <c r="T15" s="15" t="e">
+        <f t="shared" ref="T15:T19" si="12">S15/R15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="16" t="e">
+        <f t="shared" ref="U15:U19" si="13">S15/P15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" s="17">
+        <v>1</v>
+      </c>
+      <c r="W15" s="17"/>
+    </row>
+    <row r="16" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="41">
+        <v>50</v>
+      </c>
+      <c r="H16" s="55"/>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="45">
+        <v>30</v>
+      </c>
+      <c r="K16" s="60"/>
+      <c r="L16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="17">
+        <v>1</v>
+      </c>
+      <c r="O16" s="47">
+        <f t="shared" ref="O16:O19" si="14">H16</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R16" s="62">
+        <f t="shared" ref="R16:R19" si="15">K16</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="61"/>
+      <c r="T16" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" s="17">
+        <v>1</v>
+      </c>
+      <c r="W16" s="17"/>
+    </row>
+    <row r="17" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="41">
+        <v>50</v>
+      </c>
+      <c r="H17" s="55"/>
+      <c r="I17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="45">
+        <v>30</v>
+      </c>
+      <c r="K17" s="60"/>
+      <c r="L17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N17" s="17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R17" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="61"/>
+      <c r="T17" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" s="17">
+        <v>1</v>
+      </c>
+      <c r="W17" s="17"/>
+    </row>
+    <row r="18" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="41">
+        <v>50</v>
+      </c>
+      <c r="H18" s="55"/>
+      <c r="I18" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="45">
+        <v>30</v>
+      </c>
+      <c r="K18" s="60"/>
+      <c r="L18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N18" s="17">
+        <v>1</v>
+      </c>
+      <c r="O18" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R18" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="61"/>
+      <c r="T18" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V18" s="17">
+        <v>1</v>
+      </c>
+      <c r="W18" s="17"/>
+    </row>
+    <row r="19" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="41">
+        <v>50</v>
+      </c>
+      <c r="H19" s="55"/>
+      <c r="I19" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="45">
+        <v>30</v>
+      </c>
+      <c r="K19" s="60"/>
+      <c r="L19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="17">
+        <v>1</v>
+      </c>
+      <c r="O19" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R19" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="61"/>
+      <c r="T19" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V19" s="17">
+        <v>1</v>
+      </c>
+      <c r="W19" s="17"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="18">
+        <f>SUM(G15:G19)</f>
+        <v>250</v>
+      </c>
+      <c r="H20" s="19">
+        <f t="shared" ref="H20:K20" si="16">SUM(H15:H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <f t="shared" si="16"/>
+        <v>150</v>
+      </c>
+      <c r="K20" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="20">
+        <f>K20/J20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="21" t="e">
+        <f>K20/H20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="22">
+        <f>AVERAGE(N15:N19)</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="18">
+        <f>SUM(O15:O19)</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="19">
+        <f t="shared" ref="P20" si="17">SUM(P15:P19)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="20" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R20" s="56">
+        <f t="shared" ref="R20:S20" si="18">SUM(R15:R19)</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="19">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="20" t="e">
+        <f>S20/R20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="21" t="e">
+        <f>S20/P20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" s="22">
+        <f>AVERAGE(V15:V19)</f>
+        <v>1</v>
+      </c>
+      <c r="W20" s="22"/>
+    </row>
+    <row r="21" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="41">
+        <v>50</v>
+      </c>
+      <c r="H21" s="55">
+        <v>14</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J21" s="45">
+        <v>60</v>
+      </c>
+      <c r="K21" s="60">
+        <v>25</v>
+      </c>
+      <c r="L21" s="15">
+        <f t="shared" si="1"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M21" s="16">
+        <f t="shared" ref="M21:M24" si="19">K21/H21</f>
+        <v>1.7857142857142858</v>
+      </c>
+      <c r="N21" s="17">
+        <v>1</v>
+      </c>
+      <c r="O21" s="47">
+        <f>H21</f>
+        <v>14</v>
+      </c>
+      <c r="P21" s="43">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="15">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="R21" s="62">
+        <f>K21</f>
+        <v>25</v>
+      </c>
+      <c r="S21" s="61">
+        <v>15</v>
+      </c>
+      <c r="T21" s="15">
+        <f t="shared" ref="T21:T24" si="20">S21/R21</f>
+        <v>0.6</v>
+      </c>
+      <c r="U21" s="16">
+        <f t="shared" ref="U21:U24" si="21">S21/P21</f>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="V21" s="17">
+        <v>1</v>
+      </c>
+      <c r="W21" s="17"/>
+    </row>
+    <row r="22" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="41">
+        <v>50</v>
+      </c>
+      <c r="H22" s="55">
+        <v>4</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J22" s="45">
+        <v>40</v>
+      </c>
+      <c r="K22" s="60">
+        <v>7</v>
+      </c>
+      <c r="L22" s="15">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M22" s="16">
+        <f t="shared" si="19"/>
+        <v>1.75</v>
+      </c>
+      <c r="N22" s="17">
+        <v>1</v>
+      </c>
+      <c r="O22" s="47">
+        <f t="shared" ref="O22:O24" si="22">H22</f>
+        <v>4</v>
+      </c>
+      <c r="P22" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="15">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="R22" s="62">
+        <f t="shared" ref="R22:R24" si="23">K22</f>
+        <v>7</v>
+      </c>
+      <c r="S22" s="61">
+        <v>6</v>
+      </c>
+      <c r="T22" s="15">
+        <f t="shared" si="20"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U22" s="16">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="V22" s="17">
+        <v>1</v>
+      </c>
+      <c r="W22" s="17"/>
+    </row>
+    <row r="23" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="41">
+        <v>50</v>
+      </c>
+      <c r="H23" s="55">
+        <v>4</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J23" s="45">
+        <v>40</v>
+      </c>
+      <c r="K23" s="60">
+        <v>7</v>
+      </c>
+      <c r="L23" s="15">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M23" s="16">
+        <f t="shared" si="19"/>
+        <v>1.75</v>
+      </c>
+      <c r="N23" s="17">
+        <v>1</v>
+      </c>
+      <c r="O23" s="47">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="P23" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="15">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="R23" s="62">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="S23" s="61">
+        <v>4</v>
+      </c>
+      <c r="T23" s="15">
+        <f t="shared" si="20"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U23" s="16">
+        <f t="shared" si="21"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="V23" s="17">
+        <v>1</v>
+      </c>
+      <c r="W23" s="17"/>
+    </row>
+    <row r="24" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="41">
+        <v>50</v>
+      </c>
+      <c r="H24" s="55">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="45">
+        <v>30</v>
+      </c>
+      <c r="K24" s="60">
+        <v>0</v>
+      </c>
+      <c r="L24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="16" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="17">
+        <v>1</v>
+      </c>
+      <c r="O24" s="47">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R24" s="62">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="61">
+        <v>0</v>
+      </c>
+      <c r="T24" s="15" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="16" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V24" s="17">
+        <v>1</v>
+      </c>
+      <c r="W24" s="17"/>
+    </row>
+    <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="23">
+        <f>SUM(G21:G24)</f>
+        <v>200</v>
+      </c>
+      <c r="H25" s="24">
+        <f t="shared" ref="H25:K25" si="24">SUM(H21:H24)</f>
+        <v>22</v>
+      </c>
+      <c r="I25" s="25">
+        <f t="shared" si="0"/>
+        <v>0.11</v>
+      </c>
+      <c r="J25" s="26">
+        <f t="shared" si="24"/>
+        <v>170</v>
+      </c>
+      <c r="K25" s="24">
+        <f t="shared" si="24"/>
+        <v>39</v>
+      </c>
+      <c r="L25" s="25">
+        <f>K25/J25</f>
+        <v>0.22941176470588234</v>
+      </c>
+      <c r="M25" s="26">
+        <f>K25/H25</f>
+        <v>1.7727272727272727</v>
+      </c>
+      <c r="N25" s="27">
+        <f>AVERAGE(N21:N24)</f>
+        <v>1</v>
+      </c>
+      <c r="O25" s="23">
+        <f>SUM(O21:O24)</f>
+        <v>22</v>
+      </c>
+      <c r="P25" s="24">
+        <f t="shared" ref="P25" si="25">SUM(P21:P24)</f>
+        <v>13</v>
+      </c>
+      <c r="Q25" s="25">
+        <f t="shared" si="3"/>
+        <v>0.59090909090909094</v>
+      </c>
+      <c r="R25" s="26">
+        <f t="shared" ref="R25:S25" si="26">SUM(R21:R24)</f>
+        <v>39</v>
+      </c>
+      <c r="S25" s="24">
+        <f t="shared" si="26"/>
+        <v>25</v>
+      </c>
+      <c r="T25" s="25">
+        <f>S25/R25</f>
+        <v>0.64102564102564108</v>
+      </c>
+      <c r="U25" s="26">
+        <f>S25/P25</f>
+        <v>1.9230769230769231</v>
+      </c>
+      <c r="V25" s="27">
+        <f>AVERAGE(V21:V24)</f>
+        <v>1</v>
+      </c>
+      <c r="W25" s="27"/>
+    </row>
+    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="34">
+        <f>+G25+G20+G14</f>
+        <v>775</v>
+      </c>
+      <c r="H26" s="35">
+        <f t="shared" ref="H26:K26" si="27">+H25+H20+H14</f>
+        <v>84</v>
+      </c>
+      <c r="I26" s="36">
+        <f t="shared" si="0"/>
+        <v>0.10838709677419354</v>
+      </c>
+      <c r="J26" s="37">
+        <f t="shared" si="27"/>
+        <v>735</v>
+      </c>
+      <c r="K26" s="35">
+        <f t="shared" si="27"/>
+        <v>289.25</v>
+      </c>
+      <c r="L26" s="36">
+        <f>K26/J26</f>
+        <v>0.39353741496598638</v>
+      </c>
+      <c r="M26" s="37">
+        <f>K26/H26</f>
+        <v>3.4434523809523809</v>
+      </c>
+      <c r="N26" s="38"/>
+      <c r="O26" s="34">
+        <f>+O25+O20+O14</f>
+        <v>84</v>
+      </c>
+      <c r="P26" s="35">
+        <f t="shared" ref="P26" si="28">+P25+P20+P14</f>
+        <v>58</v>
+      </c>
+      <c r="Q26" s="36">
+        <f t="shared" si="3"/>
+        <v>0.69047619047619047</v>
+      </c>
+      <c r="R26" s="37">
+        <f t="shared" ref="R26:S26" si="29">+R25+R20+R14</f>
+        <v>289.25</v>
+      </c>
+      <c r="S26" s="35">
+        <f t="shared" si="29"/>
+        <v>207.5</v>
+      </c>
+      <c r="T26" s="36">
+        <f>S26/R26</f>
+        <v>0.71737251512532407</v>
+      </c>
+      <c r="U26" s="37">
+        <f>S26/P26</f>
+        <v>3.5775862068965516</v>
+      </c>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C5516F7-6F3B-4807-80F6-5003860986DF}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1183,54 +3108,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="76"/>
+      <c r="G1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="80"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="80" t="s">
+      <c r="H2" s="71"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="80"/>
-      <c r="L2" s="81"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="79" t="s">
+      <c r="O2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="80" t="s">
+      <c r="P2" s="71"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="80"/>
-      <c r="T2" s="81"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="72"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -1988,27 +3913,31 @@
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="P12" s="43"/>
+      <c r="P12" s="43">
+        <v>16</v>
+      </c>
       <c r="Q12" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="58">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="S12" s="61"/>
+      <c r="S12" s="61">
+        <v>21</v>
+      </c>
       <c r="T12" s="15">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="16" t="e">
+        <v>1</v>
+      </c>
+      <c r="U12" s="16">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V12" s="17" t="e">
+        <v>1.3125</v>
+      </c>
+      <c r="V12" s="17">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="W12" s="17"/>
     </row>
@@ -2101,11 +4030,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="66"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -2144,11 +4073,11 @@
       </c>
       <c r="P14" s="19">
         <f t="shared" ref="P14" si="9">SUM(P4:P13)</f>
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q14" s="20">
         <f t="shared" si="3"/>
-        <v>0.41935483870967744</v>
+        <v>0.67741935483870963</v>
       </c>
       <c r="R14" s="64">
         <f t="shared" ref="R14:S14" si="10">SUM(R4:R13)</f>
@@ -2156,15 +4085,15 @@
       </c>
       <c r="S14" s="63">
         <f t="shared" si="10"/>
-        <v>81.45</v>
+        <v>102.45</v>
       </c>
       <c r="T14" s="20">
         <f>S14/R14</f>
-        <v>0.30477081384471472</v>
+        <v>0.38334892422825073</v>
       </c>
       <c r="U14" s="21">
         <f>S14/P14</f>
-        <v>3.1326923076923077</v>
+        <v>2.4392857142857145</v>
       </c>
       <c r="V14" s="22" t="e">
         <f>AVERAGE(V4:V13)</f>
@@ -2537,11 +4466,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -2926,11 +4855,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -3001,13 +4930,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>
@@ -3043,11 +4972,11 @@
       </c>
       <c r="P26" s="35">
         <f t="shared" ref="P26" si="28">+P25+P20+P14</f>
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="Q26" s="36">
         <f t="shared" si="3"/>
-        <v>0.24840764331210191</v>
+        <v>0.3503184713375796</v>
       </c>
       <c r="R26" s="37">
         <f t="shared" ref="R26:S26" si="29">+R25+R20+R14</f>
@@ -3055,38 +4984,38 @@
       </c>
       <c r="S26" s="35">
         <f t="shared" si="29"/>
-        <v>106.45</v>
+        <v>127.45</v>
       </c>
       <c r="T26" s="36">
         <f>S26/R26</f>
-        <v>0.3475918367346939</v>
+        <v>0.41616326530612247</v>
       </c>
       <c r="U26" s="37">
         <f>S26/P26</f>
-        <v>2.7294871794871796</v>
+        <v>2.3172727272727274</v>
       </c>
       <c r="V26" s="38"/>
       <c r="W26" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C674A7-3942-47E0-8E65-980F1C82B5F1}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3110,54 +5039,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="76"/>
+      <c r="G1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="80"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="80" t="s">
+      <c r="H2" s="71"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="80"/>
-      <c r="L2" s="81"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="79" t="s">
+      <c r="O2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="80" t="s">
+      <c r="P2" s="71"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="80"/>
-      <c r="T2" s="81"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="72"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -4024,11 +5953,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="66"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -4490,11 +6419,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -4879,11 +6808,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -4954,13 +6883,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>
@@ -5023,23 +6952,23 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G1:N1"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5063,54 +6992,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75"/>
-      <c r="V1" s="76"/>
+      <c r="G1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="80"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="80" t="s">
+      <c r="H2" s="71"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="80"/>
-      <c r="L2" s="81"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="72"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="79" t="s">
+      <c r="O2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="80" t="s">
+      <c r="P2" s="71"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="80"/>
-      <c r="T2" s="81"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="72"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -5985,11 +7914,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="65"/>
-      <c r="F14" s="66"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -6441,11 +8370,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="65" t="s">
+      <c r="D20" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="74"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -6822,11 +8751,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -6897,13 +8826,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>
@@ -6966,17 +8895,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="G1:N1"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="E2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sales Reporting PPL - Rana Bilal Lahore (1).xlsx
+++ b/Sales Reporting PPL - Rana Bilal Lahore (1).xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AB3236-7793-4FDE-8F79-EAA58159FAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1306BFA7-5F96-4BB1-AB5A-7ACE66ABECC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="(25-06-26)" sheetId="5" r:id="rId1"/>
-    <sheet name="(24-06-26)" sheetId="4" r:id="rId2"/>
-    <sheet name="(23-06-26)" sheetId="3" r:id="rId3"/>
-    <sheet name="(22-06-26)" sheetId="1" r:id="rId4"/>
+    <sheet name="(30-06-26)" sheetId="6" r:id="rId1"/>
+    <sheet name="(25-06-26)" sheetId="5" r:id="rId2"/>
+    <sheet name="(24-06-26)" sheetId="4" r:id="rId3"/>
+    <sheet name="(23-06-26)" sheetId="3" r:id="rId4"/>
+    <sheet name="(22-06-26)" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="55">
   <si>
     <t>Booking</t>
   </si>
@@ -189,7 +190,10 @@
     <t>24-06-26</t>
   </si>
   <si>
-    <t>25-06-26</t>
+    <t>27-06-26</t>
+  </si>
+  <si>
+    <t>30-06-26</t>
   </si>
 </sst>
 </file>
@@ -833,30 +837,6 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -882,6 +862,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1164,6 +1168,1903 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D19C3EBB-D543-4E9A-8C26-8673C5556624}">
+  <dimension ref="A1:W26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.453125" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.1796875" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.7265625" customWidth="1"/>
+    <col min="20" max="21" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
+    </row>
+    <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E2" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="R3" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="40">
+        <v>50</v>
+      </c>
+      <c r="H4" s="54">
+        <v>20</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" ref="I4:I26" si="0">H4/G4</f>
+        <v>0.4</v>
+      </c>
+      <c r="J4" s="44">
+        <v>40</v>
+      </c>
+      <c r="K4" s="57">
+        <v>22.3</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" ref="L4:L24" si="1">K4/J4</f>
+        <v>0.5575</v>
+      </c>
+      <c r="M4" s="11">
+        <f t="shared" ref="M4:N13" si="2">K4/H4</f>
+        <v>1.115</v>
+      </c>
+      <c r="N4" s="12">
+        <f t="shared" si="2"/>
+        <v>1.3937499999999998</v>
+      </c>
+      <c r="O4" s="46">
+        <f>H4</f>
+        <v>20</v>
+      </c>
+      <c r="P4" s="42">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="10">
+        <f t="shared" ref="Q4:Q26" si="3">P4/O4</f>
+        <v>0.85</v>
+      </c>
+      <c r="R4" s="58">
+        <f>K4</f>
+        <v>22.3</v>
+      </c>
+      <c r="S4" s="59">
+        <v>17.8</v>
+      </c>
+      <c r="T4" s="10">
+        <f t="shared" ref="T4:T13" si="4">S4/R4</f>
+        <v>0.7982062780269058</v>
+      </c>
+      <c r="U4" s="11">
+        <f t="shared" ref="U4:V13" si="5">S4/P4</f>
+        <v>1.0470588235294118</v>
+      </c>
+      <c r="V4" s="12">
+        <f t="shared" si="5"/>
+        <v>0.93906620944341856</v>
+      </c>
+      <c r="W4" s="12"/>
+    </row>
+    <row r="5" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="41">
+        <v>50</v>
+      </c>
+      <c r="H5" s="55">
+        <v>5</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="45">
+        <v>30</v>
+      </c>
+      <c r="K5" s="60">
+        <v>3.8</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="1"/>
+        <v>0.12666666666666665</v>
+      </c>
+      <c r="M5" s="16">
+        <f t="shared" si="2"/>
+        <v>0.76</v>
+      </c>
+      <c r="N5" s="17">
+        <f t="shared" si="2"/>
+        <v>1.2666666666666664</v>
+      </c>
+      <c r="O5" s="46">
+        <f t="shared" ref="O5:O13" si="6">H5</f>
+        <v>5</v>
+      </c>
+      <c r="P5" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="15">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="R5" s="58">
+        <f t="shared" ref="R5:R13" si="7">K5</f>
+        <v>3.8</v>
+      </c>
+      <c r="S5" s="61">
+        <v>2.75</v>
+      </c>
+      <c r="T5" s="15">
+        <f t="shared" si="4"/>
+        <v>0.72368421052631582</v>
+      </c>
+      <c r="U5" s="16">
+        <f t="shared" si="5"/>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="V5" s="17">
+        <f t="shared" si="5"/>
+        <v>1.2061403508771931</v>
+      </c>
+      <c r="W5" s="17"/>
+    </row>
+    <row r="6" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="41">
+        <v>50</v>
+      </c>
+      <c r="H6" s="55">
+        <v>8</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.16</v>
+      </c>
+      <c r="J6" s="45">
+        <v>25</v>
+      </c>
+      <c r="K6" s="60">
+        <v>11.25</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="M6" s="16">
+        <f t="shared" si="2"/>
+        <v>1.40625</v>
+      </c>
+      <c r="N6" s="17">
+        <f t="shared" si="2"/>
+        <v>2.8125</v>
+      </c>
+      <c r="O6" s="46">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="P6" s="43">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="R6" s="58">
+        <f t="shared" si="7"/>
+        <v>11.25</v>
+      </c>
+      <c r="S6" s="61">
+        <v>9</v>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="U6" s="16">
+        <f t="shared" si="5"/>
+        <v>2.25</v>
+      </c>
+      <c r="V6" s="17">
+        <f t="shared" si="5"/>
+        <v>1.6</v>
+      </c>
+      <c r="W6" s="17"/>
+    </row>
+    <row r="7" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="41">
+        <v>50</v>
+      </c>
+      <c r="H7" s="55"/>
+      <c r="I7" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="45">
+        <v>30</v>
+      </c>
+      <c r="K7" s="60"/>
+      <c r="L7" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O7" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R7" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="61"/>
+      <c r="T7" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V7" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W7" s="17"/>
+    </row>
+    <row r="8" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="41">
+        <v>50</v>
+      </c>
+      <c r="H8" s="55">
+        <v>10</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="J8" s="45">
+        <v>20</v>
+      </c>
+      <c r="K8" s="60">
+        <v>12.05</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="1"/>
+        <v>0.60250000000000004</v>
+      </c>
+      <c r="M8" s="16">
+        <f t="shared" si="2"/>
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="N8" s="17">
+        <f t="shared" si="2"/>
+        <v>3.0125000000000002</v>
+      </c>
+      <c r="O8" s="46">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="P8" s="43">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="15">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="R8" s="58">
+        <f t="shared" si="7"/>
+        <v>12.05</v>
+      </c>
+      <c r="S8" s="61">
+        <v>4.55</v>
+      </c>
+      <c r="T8" s="15">
+        <f t="shared" si="4"/>
+        <v>0.37759336099585056</v>
+      </c>
+      <c r="U8" s="16">
+        <f t="shared" si="5"/>
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="V8" s="17">
+        <f t="shared" si="5"/>
+        <v>0.62932226832641758</v>
+      </c>
+      <c r="W8" s="17"/>
+    </row>
+    <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="41">
+        <v>0</v>
+      </c>
+      <c r="H9" s="55"/>
+      <c r="I9" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="45">
+        <v>20</v>
+      </c>
+      <c r="K9" s="60"/>
+      <c r="L9" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N9" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O9" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="61"/>
+      <c r="T9" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U9" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W9" s="17"/>
+    </row>
+    <row r="10" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="41">
+        <v>0</v>
+      </c>
+      <c r="H10" s="55"/>
+      <c r="I10" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J10" s="45">
+        <v>0</v>
+      </c>
+      <c r="K10" s="60"/>
+      <c r="L10" s="15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="61"/>
+      <c r="T10" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W10" s="17"/>
+    </row>
+    <row r="11" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="41">
+        <v>25</v>
+      </c>
+      <c r="H11" s="55">
+        <v>20</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="J11" s="45">
+        <v>200</v>
+      </c>
+      <c r="K11" s="60">
+        <v>150</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="M11" s="16">
+        <f t="shared" si="2"/>
+        <v>7.5</v>
+      </c>
+      <c r="N11" s="17">
+        <f t="shared" si="2"/>
+        <v>0.9375</v>
+      </c>
+      <c r="O11" s="46">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="P11" s="43">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="15">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="R11" s="58">
+        <f t="shared" si="7"/>
+        <v>150</v>
+      </c>
+      <c r="S11" s="61">
+        <v>70</v>
+      </c>
+      <c r="T11" s="15">
+        <f t="shared" si="4"/>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="U11" s="16">
+        <f t="shared" si="5"/>
+        <v>5.833333333333333</v>
+      </c>
+      <c r="V11" s="17">
+        <f t="shared" si="5"/>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="W11" s="17"/>
+    </row>
+    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="41">
+        <v>50</v>
+      </c>
+      <c r="H12" s="55">
+        <v>16</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="0"/>
+        <v>0.32</v>
+      </c>
+      <c r="J12" s="45">
+        <v>30</v>
+      </c>
+      <c r="K12" s="60">
+        <v>21</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="M12" s="16">
+        <f t="shared" si="2"/>
+        <v>1.3125</v>
+      </c>
+      <c r="N12" s="17">
+        <f t="shared" si="2"/>
+        <v>2.1875</v>
+      </c>
+      <c r="O12" s="46">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="P12" s="43">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="15">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="R12" s="58">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="S12" s="61">
+        <v>21</v>
+      </c>
+      <c r="T12" s="15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="U12" s="16">
+        <f t="shared" si="5"/>
+        <v>1.3125</v>
+      </c>
+      <c r="V12" s="17">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W12" s="17"/>
+    </row>
+    <row r="13" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="41">
+        <v>0</v>
+      </c>
+      <c r="H13" s="55">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J13" s="45">
+        <v>0</v>
+      </c>
+      <c r="K13" s="60">
+        <v>0</v>
+      </c>
+      <c r="L13" s="15" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M13" s="16" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N13" s="17" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O13" s="46">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R13" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="61">
+        <v>0</v>
+      </c>
+      <c r="T13" s="15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U13" s="16" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V13" s="17" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W13" s="17"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="18">
+        <f>SUM(G4:G13)</f>
+        <v>325</v>
+      </c>
+      <c r="H14" s="19">
+        <f t="shared" ref="H14:K14" si="8">SUM(H4:H13)</f>
+        <v>79</v>
+      </c>
+      <c r="I14" s="20">
+        <f t="shared" si="0"/>
+        <v>0.24307692307692308</v>
+      </c>
+      <c r="J14" s="21">
+        <f t="shared" si="8"/>
+        <v>395</v>
+      </c>
+      <c r="K14" s="63">
+        <f t="shared" si="8"/>
+        <v>220.4</v>
+      </c>
+      <c r="L14" s="20">
+        <f>K14/J14</f>
+        <v>0.5579746835443038</v>
+      </c>
+      <c r="M14" s="21">
+        <f>K14/H14</f>
+        <v>2.7898734177215192</v>
+      </c>
+      <c r="N14" s="22" t="e">
+        <f>AVERAGE(N4:N13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O14" s="18">
+        <f>SUM(O4:O13)</f>
+        <v>79</v>
+      </c>
+      <c r="P14" s="19">
+        <f t="shared" ref="P14" si="9">SUM(P4:P13)</f>
+        <v>58</v>
+      </c>
+      <c r="Q14" s="20">
+        <f t="shared" si="3"/>
+        <v>0.73417721518987344</v>
+      </c>
+      <c r="R14" s="64">
+        <f t="shared" ref="R14:S14" si="10">SUM(R4:R13)</f>
+        <v>220.4</v>
+      </c>
+      <c r="S14" s="63">
+        <f t="shared" si="10"/>
+        <v>125.1</v>
+      </c>
+      <c r="T14" s="20">
+        <f>S14/R14</f>
+        <v>0.56760435571687839</v>
+      </c>
+      <c r="U14" s="21">
+        <f>S14/P14</f>
+        <v>2.1568965517241376</v>
+      </c>
+      <c r="V14" s="22" t="e">
+        <f>AVERAGE(V4:V13)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W14" s="22"/>
+    </row>
+    <row r="15" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="41">
+        <v>50</v>
+      </c>
+      <c r="H15" s="55"/>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="45">
+        <v>30</v>
+      </c>
+      <c r="K15" s="60"/>
+      <c r="L15" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="16" t="e">
+        <f t="shared" ref="M15:M19" si="11">K15/H15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N15" s="17">
+        <v>1</v>
+      </c>
+      <c r="O15" s="47">
+        <f>H15</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R15" s="62">
+        <f>K15</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="61"/>
+      <c r="T15" s="15" t="e">
+        <f t="shared" ref="T15:T19" si="12">S15/R15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" s="16" t="e">
+        <f t="shared" ref="U15:U19" si="13">S15/P15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" s="17">
+        <v>1</v>
+      </c>
+      <c r="W15" s="17"/>
+    </row>
+    <row r="16" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="41">
+        <v>50</v>
+      </c>
+      <c r="H16" s="55"/>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="45">
+        <v>30</v>
+      </c>
+      <c r="K16" s="60"/>
+      <c r="L16" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="17">
+        <v>1</v>
+      </c>
+      <c r="O16" s="47">
+        <f t="shared" ref="O16:O19" si="14">H16</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R16" s="62">
+        <f t="shared" ref="R16:R19" si="15">K16</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="61"/>
+      <c r="T16" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U16" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V16" s="17">
+        <v>1</v>
+      </c>
+      <c r="W16" s="17"/>
+    </row>
+    <row r="17" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="41">
+        <v>50</v>
+      </c>
+      <c r="H17" s="55"/>
+      <c r="I17" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="45">
+        <v>30</v>
+      </c>
+      <c r="K17" s="60"/>
+      <c r="L17" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N17" s="17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R17" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="61"/>
+      <c r="T17" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U17" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V17" s="17">
+        <v>1</v>
+      </c>
+      <c r="W17" s="17"/>
+    </row>
+    <row r="18" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="41">
+        <v>50</v>
+      </c>
+      <c r="H18" s="55"/>
+      <c r="I18" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="45">
+        <v>30</v>
+      </c>
+      <c r="K18" s="60"/>
+      <c r="L18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N18" s="17">
+        <v>1</v>
+      </c>
+      <c r="O18" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R18" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="61"/>
+      <c r="T18" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U18" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V18" s="17">
+        <v>1</v>
+      </c>
+      <c r="W18" s="17"/>
+    </row>
+    <row r="19" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="41">
+        <v>50</v>
+      </c>
+      <c r="H19" s="55"/>
+      <c r="I19" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="45">
+        <v>30</v>
+      </c>
+      <c r="K19" s="60"/>
+      <c r="L19" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="16" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="17">
+        <v>1</v>
+      </c>
+      <c r="O19" s="47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R19" s="62">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="61"/>
+      <c r="T19" s="15" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" s="16" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V19" s="17">
+        <v>1</v>
+      </c>
+      <c r="W19" s="17"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="18">
+        <f>SUM(G15:G19)</f>
+        <v>250</v>
+      </c>
+      <c r="H20" s="19">
+        <f t="shared" ref="H20:K20" si="16">SUM(H15:H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <f t="shared" si="16"/>
+        <v>150</v>
+      </c>
+      <c r="K20" s="19">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="20">
+        <f>K20/J20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="21" t="e">
+        <f>K20/H20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="22">
+        <f>AVERAGE(N15:N19)</f>
+        <v>1</v>
+      </c>
+      <c r="O20" s="18">
+        <f>SUM(O15:O19)</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="19">
+        <f t="shared" ref="P20" si="17">SUM(P15:P19)</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="20" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R20" s="56">
+        <f t="shared" ref="R20:S20" si="18">SUM(R15:R19)</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="19">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="20" t="e">
+        <f>S20/R20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" s="21" t="e">
+        <f>S20/P20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" s="22">
+        <f>AVERAGE(V15:V19)</f>
+        <v>1</v>
+      </c>
+      <c r="W20" s="22"/>
+    </row>
+    <row r="21" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="41">
+        <v>50</v>
+      </c>
+      <c r="H21" s="55">
+        <v>14</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J21" s="45">
+        <v>60</v>
+      </c>
+      <c r="K21" s="60">
+        <v>25</v>
+      </c>
+      <c r="L21" s="15">
+        <f t="shared" si="1"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M21" s="16">
+        <f t="shared" ref="M21:M24" si="19">K21/H21</f>
+        <v>1.7857142857142858</v>
+      </c>
+      <c r="N21" s="17">
+        <v>1</v>
+      </c>
+      <c r="O21" s="47">
+        <f>H21</f>
+        <v>14</v>
+      </c>
+      <c r="P21" s="43">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="15">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="R21" s="62">
+        <f>K21</f>
+        <v>25</v>
+      </c>
+      <c r="S21" s="61">
+        <v>15</v>
+      </c>
+      <c r="T21" s="15">
+        <f t="shared" ref="T21:T24" si="20">S21/R21</f>
+        <v>0.6</v>
+      </c>
+      <c r="U21" s="16">
+        <f t="shared" ref="U21:U24" si="21">S21/P21</f>
+        <v>2.1428571428571428</v>
+      </c>
+      <c r="V21" s="17">
+        <v>1</v>
+      </c>
+      <c r="W21" s="17"/>
+    </row>
+    <row r="22" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="41">
+        <v>50</v>
+      </c>
+      <c r="H22" s="55">
+        <v>4</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J22" s="45">
+        <v>40</v>
+      </c>
+      <c r="K22" s="60">
+        <v>7</v>
+      </c>
+      <c r="L22" s="15">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M22" s="16">
+        <f t="shared" si="19"/>
+        <v>1.75</v>
+      </c>
+      <c r="N22" s="17">
+        <v>1</v>
+      </c>
+      <c r="O22" s="47">
+        <f t="shared" ref="O22:O24" si="22">H22</f>
+        <v>4</v>
+      </c>
+      <c r="P22" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="15">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="R22" s="62">
+        <f t="shared" ref="R22:R24" si="23">K22</f>
+        <v>7</v>
+      </c>
+      <c r="S22" s="61">
+        <v>6</v>
+      </c>
+      <c r="T22" s="15">
+        <f t="shared" si="20"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U22" s="16">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="V22" s="17">
+        <v>1</v>
+      </c>
+      <c r="W22" s="17"/>
+    </row>
+    <row r="23" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="41">
+        <v>50</v>
+      </c>
+      <c r="H23" s="55">
+        <v>4</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J23" s="45">
+        <v>40</v>
+      </c>
+      <c r="K23" s="60">
+        <v>7</v>
+      </c>
+      <c r="L23" s="15">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M23" s="16">
+        <f t="shared" si="19"/>
+        <v>1.75</v>
+      </c>
+      <c r="N23" s="17">
+        <v>1</v>
+      </c>
+      <c r="O23" s="47">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="P23" s="43">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="15">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="R23" s="62">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="S23" s="61">
+        <v>4</v>
+      </c>
+      <c r="T23" s="15">
+        <f t="shared" si="20"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U23" s="16">
+        <f t="shared" si="21"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="V23" s="17">
+        <v>1</v>
+      </c>
+      <c r="W23" s="17"/>
+    </row>
+    <row r="24" spans="1:23" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="41">
+        <v>50</v>
+      </c>
+      <c r="H24" s="55">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="45">
+        <v>30</v>
+      </c>
+      <c r="K24" s="60">
+        <v>0</v>
+      </c>
+      <c r="L24" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="16" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="17">
+        <v>1</v>
+      </c>
+      <c r="O24" s="47">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="15" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R24" s="62">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="61">
+        <v>0</v>
+      </c>
+      <c r="T24" s="15" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U24" s="16" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V24" s="17">
+        <v>1</v>
+      </c>
+      <c r="W24" s="17"/>
+    </row>
+    <row r="25" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="23">
+        <f>SUM(G21:G24)</f>
+        <v>200</v>
+      </c>
+      <c r="H25" s="24">
+        <f t="shared" ref="H25:K25" si="24">SUM(H21:H24)</f>
+        <v>22</v>
+      </c>
+      <c r="I25" s="25">
+        <f t="shared" si="0"/>
+        <v>0.11</v>
+      </c>
+      <c r="J25" s="26">
+        <f t="shared" si="24"/>
+        <v>170</v>
+      </c>
+      <c r="K25" s="24">
+        <f t="shared" si="24"/>
+        <v>39</v>
+      </c>
+      <c r="L25" s="25">
+        <f>K25/J25</f>
+        <v>0.22941176470588234</v>
+      </c>
+      <c r="M25" s="26">
+        <f>K25/H25</f>
+        <v>1.7727272727272727</v>
+      </c>
+      <c r="N25" s="27">
+        <f>AVERAGE(N21:N24)</f>
+        <v>1</v>
+      </c>
+      <c r="O25" s="23">
+        <f>SUM(O21:O24)</f>
+        <v>22</v>
+      </c>
+      <c r="P25" s="24">
+        <f t="shared" ref="P25" si="25">SUM(P21:P24)</f>
+        <v>13</v>
+      </c>
+      <c r="Q25" s="25">
+        <f t="shared" si="3"/>
+        <v>0.59090909090909094</v>
+      </c>
+      <c r="R25" s="26">
+        <f t="shared" ref="R25:S25" si="26">SUM(R21:R24)</f>
+        <v>39</v>
+      </c>
+      <c r="S25" s="24">
+        <f t="shared" si="26"/>
+        <v>25</v>
+      </c>
+      <c r="T25" s="25">
+        <f>S25/R25</f>
+        <v>0.64102564102564108</v>
+      </c>
+      <c r="U25" s="26">
+        <f>S25/P25</f>
+        <v>1.9230769230769231</v>
+      </c>
+      <c r="V25" s="27">
+        <f>AVERAGE(V21:V24)</f>
+        <v>1</v>
+      </c>
+      <c r="W25" s="27"/>
+    </row>
+    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="34">
+        <f>+G25+G20+G14</f>
+        <v>775</v>
+      </c>
+      <c r="H26" s="35">
+        <f t="shared" ref="H26:K26" si="27">+H25+H20+H14</f>
+        <v>101</v>
+      </c>
+      <c r="I26" s="36">
+        <f t="shared" si="0"/>
+        <v>0.13032258064516128</v>
+      </c>
+      <c r="J26" s="37">
+        <f t="shared" si="27"/>
+        <v>715</v>
+      </c>
+      <c r="K26" s="35">
+        <f t="shared" si="27"/>
+        <v>259.39999999999998</v>
+      </c>
+      <c r="L26" s="36">
+        <f>K26/J26</f>
+        <v>0.36279720279720279</v>
+      </c>
+      <c r="M26" s="37">
+        <f>K26/H26</f>
+        <v>2.5683168316831679</v>
+      </c>
+      <c r="N26" s="38"/>
+      <c r="O26" s="34">
+        <f>+O25+O20+O14</f>
+        <v>101</v>
+      </c>
+      <c r="P26" s="35">
+        <f t="shared" ref="P26" si="28">+P25+P20+P14</f>
+        <v>71</v>
+      </c>
+      <c r="Q26" s="36">
+        <f t="shared" si="3"/>
+        <v>0.70297029702970293</v>
+      </c>
+      <c r="R26" s="37">
+        <f t="shared" ref="R26:S26" si="29">+R25+R20+R14</f>
+        <v>259.39999999999998</v>
+      </c>
+      <c r="S26" s="35">
+        <f t="shared" si="29"/>
+        <v>150.1</v>
+      </c>
+      <c r="T26" s="36">
+        <f>S26/R26</f>
+        <v>0.57864302235929066</v>
+      </c>
+      <c r="U26" s="37">
+        <f>S26/P26</f>
+        <v>2.1140845070422536</v>
+      </c>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB43984-EA48-457F-9A17-F0D733832855}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1187,54 +3088,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="67"/>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="71" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="71"/>
-      <c r="L2" s="72"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="70" t="s">
+      <c r="O2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="71" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="71"/>
-      <c r="T2" s="72"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -2109,11 +4010,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>325</v>
@@ -2535,11 +4436,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="73" t="s">
+      <c r="D20" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -2924,11 +4825,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -2999,13 +4900,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>775</v>
@@ -3068,23 +4969,23 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G1:N1"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C5516F7-6F3B-4807-80F6-5003860986DF}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3108,54 +5009,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="67"/>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="71" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="71"/>
-      <c r="L2" s="72"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="70" t="s">
+      <c r="O2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="71" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="71"/>
-      <c r="T2" s="72"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -4030,11 +5931,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -4466,11 +6367,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="73" t="s">
+      <c r="D20" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -4855,11 +6756,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -4930,13 +6831,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>
@@ -4999,23 +6900,23 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G1:N1"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C674A7-3942-47E0-8E65-980F1C82B5F1}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5039,54 +6940,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="67"/>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="71" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="71"/>
-      <c r="L2" s="72"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="70" t="s">
+      <c r="O2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="71" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="71"/>
-      <c r="T2" s="72"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -5953,11 +7854,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -6419,11 +8320,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="73" t="s">
+      <c r="D20" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -6808,11 +8709,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -6883,13 +8784,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>
@@ -6952,23 +8853,23 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="G1:N1"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="G1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6992,54 +8893,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="67"/>
+      <c r="G1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="69"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="71" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="71"/>
-      <c r="L2" s="72"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="70" t="s">
+      <c r="O2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="71" t="s">
+      <c r="P2" s="80"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="71"/>
-      <c r="T2" s="72"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="81"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -7914,11 +9815,11 @@
       <c r="C14" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="73"/>
-      <c r="F14" s="74"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="66"/>
       <c r="G14" s="18">
         <f>SUM(G4:G13)</f>
         <v>310</v>
@@ -8370,11 +10271,11 @@
       <c r="C20" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="73" t="s">
+      <c r="D20" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="18">
         <f>SUM(G15:G19)</f>
         <v>250</v>
@@ -8751,11 +10652,11 @@
       <c r="C25" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="23">
         <f>SUM(G21:G24)</f>
         <v>200</v>
@@ -8826,13 +10727,13 @@
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
       <c r="G26" s="34">
         <f>+G25+G20+G14</f>
         <v>760</v>
@@ -8895,17 +10796,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="G1:N1"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="E2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
